--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7442,0.1131,0.0537,0.0462</t>
-  </si>
-  <si>
-    <t>0.8999,0.0099,0.0058,0.0408</t>
-  </si>
-  <si>
-    <t>0.8448,0.0549,0.0286,0.0311</t>
-  </si>
-  <si>
-    <t>0.7137,0.0338,0.0031,0.0752</t>
-  </si>
-  <si>
-    <t>0.8559,0.0162,0.0056,0.0666</t>
-  </si>
-  <si>
-    <t>0.8549,0.0465,0.0055,0.0137</t>
-  </si>
-  <si>
-    <t>0.7316,0.1100,0.0221,0.0398</t>
-  </si>
-  <si>
-    <t>0.8053,0.0425,0.0030,0.0284</t>
-  </si>
-  <si>
-    <t>0.4620,0.0956,0.0361,0.2743</t>
-  </si>
-  <si>
-    <t>0.8613,0.0235,0.0069,0.0429</t>
-  </si>
-  <si>
-    <t>0.6976,0.1762,0.0413,0.0324</t>
-  </si>
-  <si>
-    <t>0.8585,0.0339,0.0100,0.0410</t>
-  </si>
-  <si>
-    <t>0.8825,0.0257,0.0196,0.0326</t>
-  </si>
-  <si>
-    <t>0.8865,0.0209,0.0742,0.0173</t>
-  </si>
-  <si>
-    <t>0.8136,0.0459,0.0548,0.0644</t>
-  </si>
-  <si>
-    <t>0.9131,0.0140,0.0554,0.0094</t>
-  </si>
-  <si>
-    <t>0.8938,0.0320,0.0069,0.0157</t>
-  </si>
-  <si>
-    <t>0.0652,0.8869,0.0321,0.0128</t>
-  </si>
-  <si>
-    <t>0.2903,0.6204,0.0313,0.0204</t>
-  </si>
-  <si>
-    <t>0.3780,0.3965,0.0269,0.0308</t>
-  </si>
-  <si>
-    <t>0.4246,0.4222,0.0348,0.0232</t>
-  </si>
-  <si>
-    <t>0.0149,0.9766,0.0032,0.0023</t>
-  </si>
-  <si>
-    <t>0.9244,0.0057,0.0543,0.0094</t>
-  </si>
-  <si>
-    <t>0.9707,0.0016,0.0183,0.0029</t>
-  </si>
-  <si>
-    <t>0.9177,0.0096,0.0971,0.0015</t>
-  </si>
-  <si>
-    <t>0.7252,0.0563,0.1559,0.0780</t>
-  </si>
-  <si>
-    <t>0.8038,0.0300,0.1493,0.0274</t>
-  </si>
-  <si>
-    <t>0.9234,0.0118,0.0196,0.0228</t>
-  </si>
-  <si>
-    <t>0.3371,0.0379,0.8218,0.0020</t>
-  </si>
-  <si>
-    <t>0.8307,0.0574,0.0104,0.0223</t>
-  </si>
-  <si>
-    <t>0.5506,0.1187,0.0723,0.2039</t>
-  </si>
-  <si>
-    <t>0.0148,0.8337,0.8937,0.0055</t>
-  </si>
-  <si>
-    <t>0.5434,0.3481,0.1224,0.0088</t>
-  </si>
-  <si>
-    <t>0.7884,0.0679,0.0154,0.0388</t>
-  </si>
-  <si>
-    <t>0.4792,0.1885,0.0441,0.0982</t>
-  </si>
-  <si>
-    <t>0.5377,0.2108,0.0413,0.0704</t>
-  </si>
-  <si>
-    <t>0.6149,0.2646,0.0116,0.0097</t>
-  </si>
-  <si>
-    <t>0.5192,0.2585,0.0812,0.0445</t>
-  </si>
-  <si>
-    <t>0.7947,0.0390,0.1374,0.0254</t>
-  </si>
-  <si>
-    <t>0.4352,0.1209,0.5513,0.0095</t>
-  </si>
-  <si>
-    <t>0.6610,0.0857,0.3139,0.0124</t>
-  </si>
-  <si>
-    <t>0.9323,0.0099,0.0492,0.0046</t>
-  </si>
-  <si>
-    <t>0.1314,0.8632,0.0937,0.0065</t>
-  </si>
-  <si>
-    <t>0.4255,0.1313,0.4982,0.0166</t>
-  </si>
-  <si>
-    <t>0.8326,0.0257,0.0147,0.0828</t>
-  </si>
-  <si>
-    <t>0.6128,0.1221,0.0502,0.0976</t>
-  </si>
-  <si>
-    <t>0.5946,0.3214,0.0722,0.0145</t>
-  </si>
-  <si>
-    <t>0.0725,0.8855,0.0971,0.0139</t>
-  </si>
-  <si>
-    <t>0.2530,0.0981,0.6861,0.0244</t>
-  </si>
-  <si>
-    <t>0.3229,0.1363,0.6702,0.0137</t>
-  </si>
-  <si>
-    <t>0.7646,0.0161,0.2891,0.0045</t>
-  </si>
-  <si>
-    <t>0.7736,0.0140,0.2645,0.0164</t>
-  </si>
-  <si>
-    <t>0.3610,0.1303,0.6554,0.0027</t>
-  </si>
-  <si>
-    <t>0.5717,0.1476,0.3508,0.0111</t>
-  </si>
-  <si>
-    <t>0.8595,0.0317,0.0051,0.0260</t>
-  </si>
-  <si>
-    <t>0.8572,0.0464,0.0093,0.0235</t>
-  </si>
-  <si>
-    <t>0.7925,0.0567,0.0094,0.0388</t>
-  </si>
-  <si>
-    <t>0.3345,0.5270,0.2530,0.0380</t>
-  </si>
-  <si>
-    <t>0.6870,0.1040,0.0174,0.0511</t>
-  </si>
-  <si>
-    <t>0.6125,0.1402,0.0274,0.0696</t>
-  </si>
-  <si>
-    <t>0.6285,0.2478,0.0444,0.0219</t>
-  </si>
-  <si>
-    <t>0.0729,0.6746,0.7550,0.0041</t>
-  </si>
-  <si>
-    <t>0.5988,0.0696,0.3509,0.0148</t>
-  </si>
-  <si>
-    <t>0.2138,0.1610,0.7938,0.0064</t>
-  </si>
-  <si>
-    <t>0.0044,0.9633,0.8645,0.0014</t>
-  </si>
-  <si>
-    <t>0.1927,0.0432,0.8534,0.0046</t>
-  </si>
-  <si>
-    <t>0.3420,0.5908,0.1002,0.0141</t>
-  </si>
-  <si>
-    <t>0.0075,0.9853,0.0397,0.0033</t>
-  </si>
-  <si>
-    <t>0.8858,0.0271,0.0036,0.0225</t>
-  </si>
-  <si>
-    <t>0.6548,0.1401,0.0403,0.0461</t>
-  </si>
-  <si>
-    <t>0.0479,0.3745,0.9373,0.0041</t>
-  </si>
-  <si>
-    <t>0.0172,0.5134,0.9560,0.0008</t>
-  </si>
-  <si>
-    <t>0.3388,0.3599,0.4501,0.0095</t>
-  </si>
-  <si>
-    <t>0.0023,0.9809,0.8017,0.0009</t>
-  </si>
-  <si>
-    <t>0.0034,0.9454,0.9176,0.0016</t>
-  </si>
-  <si>
-    <t>0.6020,0.0744,0.1024,0.2362</t>
-  </si>
-  <si>
-    <t>0.7703,0.0462,0.0227,0.0815</t>
-  </si>
-  <si>
-    <t>0.9099,0.0146,0.0045,0.0268</t>
-  </si>
-  <si>
-    <t>0.6757,0.0869,0.0652,0.1748</t>
-  </si>
-  <si>
-    <t>0.7891,0.0470,0.0285,0.0659</t>
-  </si>
-  <si>
-    <t>0.9308,0.0115,0.0129,0.0295</t>
-  </si>
-  <si>
-    <t>0.1254,0.5953,0.6180,0.0184</t>
-  </si>
-  <si>
-    <t>0.0941,0.3806,0.8338,0.0056</t>
-  </si>
-  <si>
-    <t>0.1157,0.5092,0.7202,0.0157</t>
-  </si>
-  <si>
-    <t>0.2146,0.3846,0.6371,0.0109</t>
-  </si>
-  <si>
-    <t>0.0243,0.9309,0.5011,0.0022</t>
-  </si>
-  <si>
-    <t>0.1872,0.6235,0.4552,0.0373</t>
-  </si>
-  <si>
-    <t>0.7733,0.0468,0.0131,0.0628</t>
-  </si>
-  <si>
-    <t>0.7244,0.1287,0.0068,0.0141</t>
-  </si>
-  <si>
-    <t>0.5558,0.2823,0.0297,0.0249</t>
-  </si>
-  <si>
-    <t>0.7723,0.0590,0.0130,0.0521</t>
-  </si>
-  <si>
-    <t>0.7972,0.0314,0.0096,0.0667</t>
-  </si>
-  <si>
-    <t>0.4761,0.1512,0.0167,0.0773</t>
-  </si>
-  <si>
-    <t>0.6478,0.1749,0.0118,0.0154</t>
-  </si>
-  <si>
-    <t>0.7343,0.0444,0.0134,0.0937</t>
-  </si>
-  <si>
-    <t>0.8781,0.0131,0.0017,0.0323</t>
-  </si>
-  <si>
-    <t>0.8016,0.0771,0.0230,0.0284</t>
-  </si>
-  <si>
-    <t>0.7388,0.1318,0.0097,0.0124</t>
-  </si>
-  <si>
-    <t>0.7579,0.0500,0.0087,0.0505</t>
-  </si>
-  <si>
-    <t>0.7950,0.0142,0.0049,0.1236</t>
-  </si>
-  <si>
-    <t>0.8091,0.0288,0.0069,0.0617</t>
-  </si>
-  <si>
-    <t>0.7692,0.0788,0.0121,0.0332</t>
-  </si>
-  <si>
-    <t>0.3890,0.2835,0.0186,0.0447</t>
-  </si>
-  <si>
-    <t>0.3272,0.1126,0.7291,0.0200</t>
-  </si>
-  <si>
-    <t>0.6536,0.0921,0.3005,0.0100</t>
-  </si>
-  <si>
-    <t>0.9214,0.0133,0.0256,0.0223</t>
-  </si>
-  <si>
-    <t>0.8034,0.0086,0.2255,0.0063</t>
-  </si>
-  <si>
-    <t>0.0135,0.9615,0.1109,0.0148</t>
-  </si>
-  <si>
-    <t>0.4269,0.3447,0.0481,0.0587</t>
-  </si>
-  <si>
-    <t>0.2736,0.6318,0.0462,0.0126</t>
-  </si>
-  <si>
-    <t>0.5626,0.3144,0.0176,0.0135</t>
-  </si>
-  <si>
-    <t>0.0493,0.9020,0.0754,0.0209</t>
-  </si>
-  <si>
-    <t>0.0166,0.9679,0.0711,0.0054</t>
-  </si>
-  <si>
-    <t>0.8281,0.0840,0.0036,0.0083</t>
-  </si>
-  <si>
-    <t>0.8042,0.0823,0.0156,0.0221</t>
-  </si>
-  <si>
-    <t>0.8529,0.0271,0.0478,0.0481</t>
-  </si>
-  <si>
-    <t>0.5998,0.1130,0.0598,0.1291</t>
-  </si>
-  <si>
-    <t>0.9051,0.0332,0.0229,0.0129</t>
-  </si>
-  <si>
-    <t>0.5244,0.0692,0.0382,0.2844</t>
-  </si>
-  <si>
-    <t>0.6033,0.2005,0.0249,0.0321</t>
-  </si>
-  <si>
-    <t>0.4084,0.4149,0.0514,0.0297</t>
-  </si>
-  <si>
-    <t>0.7969,0.0230,0.0173,0.1101</t>
-  </si>
-  <si>
-    <t>0.0245,0.9401,0.4515,0.0159</t>
-  </si>
-  <si>
-    <t>0.1431,0.8027,0.0450,0.0107</t>
-  </si>
-  <si>
-    <t>0.4288,0.3040,0.0259,0.0362</t>
-  </si>
-  <si>
-    <t>0.7548,0.0649,0.0165,0.0483</t>
-  </si>
-  <si>
-    <t>0.8178,0.0507,0.0064,0.0237</t>
-  </si>
-  <si>
-    <t>0.9030,0.0268,0.0057,0.0171</t>
-  </si>
-  <si>
-    <t>0.8094,0.0615,0.0084,0.0286</t>
-  </si>
-  <si>
-    <t>0.7804,0.0865,0.0132,0.0310</t>
-  </si>
-  <si>
-    <t>0.6688,0.1403,0.0294,0.0477</t>
-  </si>
-  <si>
-    <t>0.8874,0.0268,0.0093,0.0275</t>
-  </si>
-  <si>
-    <t>0.8631,0.0412,0.0117,0.0233</t>
-  </si>
-  <si>
-    <t>0.7557,0.0474,0.0105,0.0431</t>
-  </si>
-  <si>
-    <t>0.2257,0.3087,0.6585,0.0168</t>
-  </si>
-  <si>
-    <t>0.6163,0.1437,0.2323,0.0096</t>
-  </si>
-  <si>
-    <t>0.7792,0.0745,0.1324,0.0072</t>
-  </si>
-  <si>
-    <t>0.6183,0.0463,0.3528,0.0148</t>
-  </si>
-  <si>
-    <t>0.8007,0.0771,0.0305,0.0271</t>
-  </si>
-  <si>
-    <t>0.9104,0.0175,0.0066,0.0224</t>
-  </si>
-  <si>
-    <t>0.4698,0.1444,0.3989,0.0801</t>
-  </si>
-  <si>
-    <t>0.9265,0.0097,0.0050,0.0242</t>
-  </si>
-  <si>
-    <t>0.8733,0.0106,0.0074,0.0709</t>
-  </si>
-  <si>
-    <t>0.6534,0.0097,0.0076,0.3598</t>
-  </si>
-  <si>
-    <t>0.8138,0.0143,0.0102,0.1448</t>
-  </si>
-  <si>
-    <t>0.6522,0.0400,0.0621,0.2566</t>
-  </si>
-  <si>
-    <t>0.0201,0.9348,0.3427,0.0227</t>
-  </si>
-  <si>
-    <t>0.8667,0.0665,0.0068,0.0144</t>
-  </si>
-  <si>
-    <t>0.5694,0.3291,0.0787,0.0168</t>
-  </si>
-  <si>
-    <t>0.9016,0.0183,0.0025,0.0203</t>
-  </si>
-  <si>
-    <t>0.5557,0.2763,0.0264,0.0167</t>
-  </si>
-  <si>
-    <t>0.6775,0.0693,0.0238,0.1036</t>
-  </si>
-  <si>
-    <t>0.8538,0.0143,0.0072,0.0700</t>
-  </si>
-  <si>
-    <t>0.8120,0.1022,0.0202,0.0224</t>
-  </si>
-  <si>
-    <t>0.0157,0.8353,0.8795,0.0141</t>
-  </si>
-  <si>
-    <t>0.9588,0.0037,0.0009,0.0150</t>
-  </si>
-  <si>
-    <t>0.7934,0.0382,0.0177,0.0681</t>
-  </si>
-  <si>
-    <t>0.4844,0.2672,0.0478,0.0579</t>
-  </si>
-  <si>
-    <t>0.6440,0.1251,0.0412,0.0791</t>
-  </si>
-  <si>
-    <t>0.6536,0.1347,0.0594,0.0823</t>
-  </si>
-  <si>
-    <t>0.4759,0.1876,0.0560,0.1110</t>
-  </si>
-  <si>
-    <t>0.8016,0.0494,0.0169,0.0503</t>
-  </si>
-  <si>
-    <t>0.5009,0.3884,0.0313,0.0166</t>
-  </si>
-  <si>
-    <t>0.7225,0.0442,0.0147,0.0965</t>
-  </si>
-  <si>
-    <t>0.5793,0.1358,0.0128,0.0523</t>
-  </si>
-  <si>
-    <t>0.7885,0.0559,0.0271,0.0675</t>
-  </si>
-  <si>
-    <t>0.8983,0.0340,0.0055,0.0157</t>
-  </si>
-  <si>
-    <t>0.5524,0.0624,0.0145,0.1822</t>
-  </si>
-  <si>
-    <t>0.7958,0.0837,0.0214,0.0299</t>
-  </si>
-  <si>
-    <t>0.8109,0.0299,0.0078,0.0630</t>
-  </si>
-  <si>
-    <t>0.7158,0.0697,0.0375,0.1075</t>
-  </si>
-  <si>
-    <t>0.4514,0.3623,0.0343,0.0288</t>
-  </si>
-  <si>
-    <t>0.6005,0.1293,0.0146,0.0444</t>
-  </si>
-  <si>
-    <t>0.6954,0.0780,0.0145,0.0757</t>
-  </si>
-  <si>
-    <t>0.7370,0.0729,0.0247,0.0651</t>
-  </si>
-  <si>
-    <t>0.7557,0.0563,0.0109,0.0536</t>
-  </si>
-  <si>
-    <t>0.7537,0.0941,0.0577,0.0628</t>
-  </si>
-  <si>
-    <t>0.6524,0.1768,0.0368,0.0454</t>
-  </si>
-  <si>
-    <t>0.7629,0.1368,0.0192,0.0206</t>
-  </si>
-  <si>
-    <t>0.1221,0.4846,0.7674,0.0124</t>
-  </si>
-  <si>
-    <t>0.7557,0.1729,0.0168,0.0116</t>
-  </si>
-  <si>
-    <t>0.1706,0.0336,0.9022,0.0020</t>
-  </si>
-  <si>
-    <t>0.8903,0.0076,0.1542,0.0026</t>
-  </si>
-  <si>
-    <t>0.9098,0.0161,0.0562,0.0094</t>
-  </si>
-  <si>
-    <t>0.2434,0.0537,0.7994,0.0025</t>
-  </si>
-  <si>
-    <t>0.4643,0.0615,0.5711,0.0143</t>
-  </si>
-  <si>
-    <t>0.8023,0.0142,0.2381,0.0099</t>
-  </si>
-  <si>
-    <t>0.3565,0.4318,0.3876,0.0152</t>
-  </si>
-  <si>
-    <t>0.8439,0.0478,0.0201,0.0342</t>
-  </si>
-  <si>
-    <t>0.9132,0.0231,0.0238,0.0124</t>
-  </si>
-  <si>
-    <t>0.6817,0.0953,0.2250,0.0529</t>
-  </si>
-  <si>
-    <t>0.9188,0.0235,0.0300,0.0093</t>
-  </si>
-  <si>
-    <t>0.9003,0.0768,0.0083,0.0052</t>
-  </si>
-  <si>
-    <t>0.6761,0.1373,0.1836,0.0240</t>
-  </si>
-  <si>
-    <t>0.7917,0.0123,0.0189,0.1894</t>
-  </si>
-  <si>
-    <t>0.8350,0.0215,0.0488,0.0503</t>
-  </si>
-  <si>
-    <t>0.4907,0.2399,0.0333,0.0688</t>
-  </si>
-  <si>
-    <t>0.4858,0.2649,0.0203,0.0449</t>
-  </si>
-  <si>
-    <t>0.5101,0.1993,0.0142,0.0386</t>
-  </si>
-  <si>
-    <t>0.8010,0.0235,0.0073,0.0702</t>
-  </si>
-  <si>
-    <t>0.6330,0.1043,0.0112,0.0483</t>
-  </si>
-  <si>
-    <t>0.9180,0.0152,0.0106,0.0218</t>
-  </si>
-  <si>
-    <t>0.9361,0.0126,0.0077,0.0129</t>
-  </si>
-  <si>
-    <t>0.7670,0.0415,0.0178,0.0841</t>
-  </si>
-  <si>
-    <t>0.8347,0.0721,0.0633,0.0166</t>
-  </si>
-  <si>
-    <t>0.8861,0.0115,0.0098,0.0541</t>
-  </si>
-  <si>
-    <t>0.1679,0.3433,0.7759,0.0176</t>
-  </si>
-  <si>
-    <t>0.7309,0.0733,0.2050,0.0173</t>
-  </si>
-  <si>
-    <t>0.7898,0.0422,0.1857,0.0058</t>
-  </si>
-  <si>
-    <t>0.5896,0.0246,0.4154,0.0274</t>
-  </si>
-  <si>
-    <t>0.6302,0.0672,0.3334,0.0041</t>
-  </si>
-  <si>
-    <t>0.7993,0.0248,0.0072,0.0629</t>
-  </si>
-  <si>
-    <t>0.7977,0.0688,0.0113,0.0269</t>
-  </si>
-  <si>
-    <t>0.8118,0.0234,0.0083,0.0796</t>
-  </si>
-  <si>
-    <t>0.6622,0.1143,0.0299,0.0863</t>
-  </si>
-  <si>
-    <t>0.8348,0.0564,0.0068,0.0185</t>
-  </si>
-  <si>
-    <t>0.8400,0.0492,0.0075,0.0232</t>
-  </si>
-  <si>
-    <t>0.8939,0.0341,0.0051,0.0151</t>
-  </si>
-  <si>
-    <t>0.8588,0.0162,0.0047,0.0560</t>
-  </si>
-  <si>
-    <t>0.7902,0.0526,0.0507,0.0789</t>
-  </si>
-  <si>
-    <t>0.8042,0.0590,0.0227,0.0472</t>
-  </si>
-  <si>
-    <t>0.7586,0.0922,0.0101,0.0246</t>
-  </si>
-  <si>
-    <t>0.6409,0.0866,0.3225,0.0198</t>
-  </si>
-  <si>
-    <t>0.0998,0.2019,0.8795,0.0147</t>
-  </si>
-  <si>
-    <t>0.3571,0.1570,0.6032,0.0123</t>
-  </si>
-  <si>
-    <t>0.0914,0.0701,0.9436,0.0015</t>
-  </si>
-  <si>
-    <t>0.8076,0.0349,0.1347,0.0162</t>
-  </si>
-  <si>
-    <t>0.0670,0.3613,0.8747,0.0194</t>
-  </si>
-  <si>
-    <t>0.2247,0.2148,0.6753,0.0323</t>
-  </si>
-  <si>
-    <t>0.3553,0.4415,0.0982,0.0596</t>
-  </si>
-  <si>
-    <t>0.9504,0.0066,0.0082,0.0118</t>
-  </si>
-  <si>
-    <t>0.8025,0.0516,0.0553,0.0552</t>
-  </si>
-  <si>
-    <t>0.9012,0.0206,0.0140,0.0272</t>
-  </si>
-  <si>
-    <t>0.8136,0.0480,0.0105,0.0396</t>
-  </si>
-  <si>
-    <t>0.8449,0.0453,0.0125,0.0282</t>
-  </si>
-  <si>
-    <t>0.8366,0.0515,0.0070,0.0181</t>
-  </si>
-  <si>
-    <t>0.7480,0.1078,0.0153,0.0230</t>
-  </si>
-  <si>
-    <t>0.7556,0.0528,0.0095,0.0462</t>
-  </si>
-  <si>
-    <t>0.8254,0.0692,0.0094,0.0173</t>
-  </si>
-  <si>
-    <t>0.8206,0.0978,0.0161,0.0188</t>
-  </si>
-  <si>
-    <t>0.7208,0.1118,0.0212,0.0499</t>
-  </si>
-  <si>
-    <t>0.6583,0.0273,0.4186,0.0041</t>
-  </si>
-  <si>
-    <t>0.1212,0.2528,0.8300,0.0103</t>
-  </si>
-  <si>
-    <t>0.4740,0.0450,0.5990,0.0075</t>
-  </si>
-  <si>
-    <t>0.9190,0.0227,0.0286,0.0075</t>
-  </si>
-  <si>
-    <t>0.6198,0.0117,0.4977,0.0043</t>
-  </si>
-  <si>
-    <t>0.8953,0.0198,0.0463,0.0109</t>
-  </si>
-  <si>
-    <t>0.5633,0.2216,0.2350,0.0229</t>
-  </si>
-  <si>
-    <t>0.6920,0.0355,0.2637,0.0398</t>
-  </si>
-  <si>
-    <t>0.9600,0.0088,0.0025,0.0072</t>
-  </si>
-  <si>
-    <t>0.8450,0.0155,0.0185,0.1030</t>
-  </si>
-  <si>
-    <t>0.9058,0.0097,0.0115,0.0642</t>
-  </si>
-  <si>
-    <t>0.6883,0.0377,0.0355,0.2101</t>
-  </si>
-  <si>
-    <t>0.8131,0.0190,0.0094,0.1186</t>
-  </si>
-  <si>
-    <t>0.8258,0.0269,0.0084,0.0498</t>
+    <t>0.9607,0.0030,0.0120,0.0167</t>
+  </si>
+  <si>
+    <t>0.0317,0.0007,0.0014,0.9884</t>
+  </si>
+  <si>
+    <t>0.4899,0.0002,0.0011,0.7963</t>
+  </si>
+  <si>
+    <t>0.1647,0.0099,0.0089,0.9078</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0007,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0001,0.0000,0.0030</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9911,0.0036,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.8523,0.0176,0.1556,0.0057</t>
+  </si>
+  <si>
+    <t>0.2316,0.0133,0.8489,0.0051</t>
+  </si>
+  <si>
+    <t>0.4521,0.0051,0.7628,0.0004</t>
+  </si>
+  <si>
+    <t>0.1017,0.0021,0.9524,0.0012</t>
+  </si>
+  <si>
+    <t>0.9459,0.0036,0.1015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9991,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.9963,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.0099,0.9843,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.9952,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.9983,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.8670,0.0029,0.2270,0.0011</t>
+  </si>
+  <si>
+    <t>0.3661,0.0144,0.7550,0.0025</t>
+  </si>
+  <si>
+    <t>0.0034,0.0050,0.9949,0.0003</t>
+  </si>
+  <si>
+    <t>0.0307,0.0148,0.9418,0.0076</t>
+  </si>
+  <si>
+    <t>0.0344,0.0233,0.9472,0.0059</t>
+  </si>
+  <si>
+    <t>0.4969,0.0238,0.5330,0.0235</t>
+  </si>
+  <si>
+    <t>0.0031,0.0041,0.9766,0.0438</t>
+  </si>
+  <si>
+    <t>0.7955,0.3036,0.0053,0.0003</t>
+  </si>
+  <si>
+    <t>0.5590,0.4294,0.0530,0.0028</t>
+  </si>
+  <si>
+    <t>0.0009,0.0310,0.9963,0.0022</t>
+  </si>
+  <si>
+    <t>0.0053,0.9670,0.1258,0.0003</t>
+  </si>
+  <si>
+    <t>0.9756,0.0047,0.0062,0.0073</t>
+  </si>
+  <si>
+    <t>0.1099,0.0115,0.8655,0.0465</t>
+  </si>
+  <si>
+    <t>0.9147,0.0905,0.0115,0.0022</t>
+  </si>
+  <si>
+    <t>0.0046,0.9913,0.0589,0.0004</t>
+  </si>
+  <si>
+    <t>0.0325,0.5017,0.5559,0.0018</t>
+  </si>
+  <si>
+    <t>0.2671,0.0030,0.7317,0.0153</t>
+  </si>
+  <si>
+    <t>0.0107,0.0022,0.9884,0.0007</t>
+  </si>
+  <si>
+    <t>0.4195,0.0021,0.8309,0.0009</t>
+  </si>
+  <si>
+    <t>0.0099,0.0604,0.9412,0.0100</t>
+  </si>
+  <si>
+    <t>0.0240,0.9662,0.0103,0.0014</t>
+  </si>
+  <si>
+    <t>0.0074,0.0036,0.9908,0.0022</t>
+  </si>
+  <si>
+    <t>0.2109,0.3838,0.0402,0.4443</t>
+  </si>
+  <si>
+    <t>0.0013,0.9928,0.0266,0.0058</t>
+  </si>
+  <si>
+    <t>0.0011,0.9945,0.0179,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.9981,0.0076,0.0014</t>
+  </si>
+  <si>
+    <t>0.0046,0.0225,0.9866,0.0063</t>
+  </si>
+  <si>
+    <t>0.0051,0.5014,0.9536,0.0013</t>
+  </si>
+  <si>
+    <t>0.0033,0.0054,0.9936,0.0008</t>
+  </si>
+  <si>
+    <t>0.0118,0.0008,0.9863,0.0036</t>
+  </si>
+  <si>
+    <t>0.0157,0.0119,0.9749,0.0074</t>
+  </si>
+  <si>
+    <t>0.0110,0.5200,0.8881,0.0007</t>
+  </si>
+  <si>
+    <t>0.9751,0.0272,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9900,0.0013,0.0046,0.0015</t>
+  </si>
+  <si>
+    <t>0.9903,0.0014,0.0005,0.0037</t>
+  </si>
+  <si>
+    <t>0.0099,0.0094,0.9828,0.0112</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9827,0.0130,0.0025,0.0019</t>
+  </si>
+  <si>
+    <t>0.9893,0.0049,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.8631,0.9917,0.0003</t>
+  </si>
+  <si>
+    <t>0.0075,0.0664,0.9636,0.0064</t>
+  </si>
+  <si>
+    <t>0.0044,0.0160,0.9863,0.0052</t>
+  </si>
+  <si>
+    <t>0.0011,0.9652,0.8959,0.0020</t>
+  </si>
+  <si>
+    <t>0.0014,0.0022,0.9967,0.0006</t>
+  </si>
+  <si>
+    <t>0.0224,0.9607,0.0074,0.0021</t>
+  </si>
+  <si>
+    <t>0.0018,0.9964,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7837,0.0042,0.3323,0.0041</t>
+  </si>
+  <si>
+    <t>0.2771,0.4760,0.5417,0.0148</t>
+  </si>
+  <si>
+    <t>0.0030,0.0026,0.9962,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.9777,0.8905,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.8968,0.5828,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.4851,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9519,0.9084,0.0011</t>
+  </si>
+  <si>
+    <t>0.0085,0.0013,0.0418,0.9750</t>
+  </si>
+  <si>
+    <t>0.0010,0.0018,0.0007,0.9990</t>
+  </si>
+  <si>
+    <t>0.0230,0.0031,0.0010,0.9908</t>
+  </si>
+  <si>
+    <t>0.0117,0.0017,0.0014,0.9947</t>
+  </si>
+  <si>
+    <t>0.0107,0.0002,0.0006,0.9964</t>
+  </si>
+  <si>
+    <t>0.0031,0.0013,0.0016,0.9972</t>
+  </si>
+  <si>
+    <t>0.0025,0.9236,0.6047,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.8418,0.9853,0.0005</t>
+  </si>
+  <si>
+    <t>0.0061,0.9410,0.5645,0.0019</t>
+  </si>
+  <si>
+    <t>0.0009,0.9367,0.9647,0.0015</t>
+  </si>
+  <si>
+    <t>0.0041,0.8793,0.8591,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.7811,0.9087,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9946,0.0023,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9859,0.0116,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9937,0.0022,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9947,0.0012,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9938,0.0019,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9899,0.0032,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9886,0.0035,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9955,0.0012,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9969,0.0001,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9910,0.0023,0.0028,0.0013</t>
+  </si>
+  <si>
+    <t>0.9942,0.0029,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9961,0.0003,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.0105,0.0063,0.9837,0.0055</t>
+  </si>
+  <si>
+    <t>0.0030,0.0033,0.9922,0.0023</t>
+  </si>
+  <si>
+    <t>0.9771,0.0048,0.0125,0.0006</t>
+  </si>
+  <si>
+    <t>0.4041,0.0014,0.8130,0.0004</t>
+  </si>
+  <si>
+    <t>0.0094,0.9843,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.9958,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0127,0.9821,0.0032,0.0017</t>
+  </si>
+  <si>
+    <t>0.0630,0.9349,0.0134,0.0022</t>
+  </si>
+  <si>
+    <t>0.0107,0.9852,0.0050,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.9949,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.9262,0.1441,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.6685,0.1787,0.1008,0.0264</t>
+  </si>
+  <si>
+    <t>0.3247,0.0010,0.7625,0.0037</t>
+  </si>
+  <si>
+    <t>0.8307,0.0127,0.2003,0.0063</t>
+  </si>
+  <si>
+    <t>0.7866,0.0077,0.3107,0.0047</t>
+  </si>
+  <si>
+    <t>0.0189,0.0714,0.0124,0.9640</t>
+  </si>
+  <si>
+    <t>0.0021,0.9906,0.0094,0.0036</t>
+  </si>
+  <si>
+    <t>0.0047,0.9889,0.0069,0.0069</t>
+  </si>
+  <si>
+    <t>0.0003,0.9968,0.0084,0.0067</t>
+  </si>
+  <si>
+    <t>0.0031,0.9593,0.6910,0.0022</t>
+  </si>
+  <si>
+    <t>0.0029,0.9959,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.6862,0.4820,0.0043,0.0007</t>
+  </si>
+  <si>
+    <t>0.8283,0.2431,0.0059,0.0028</t>
+  </si>
+  <si>
+    <t>0.9935,0.0010,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9952,0.0009,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.9930,0.0007,0.0007,0.0032</t>
+  </si>
+  <si>
+    <t>0.9935,0.0008,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.9935,0.0006,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9966,0.0002,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9945,0.0015,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0021,0.8447,0.9698,0.0008</t>
+  </si>
+  <si>
+    <t>0.0018,0.5755,0.9661,0.0005</t>
+  </si>
+  <si>
+    <t>0.0105,0.0819,0.9642,0.0005</t>
+  </si>
+  <si>
+    <t>0.1054,0.1034,0.7757,0.0020</t>
+  </si>
+  <si>
+    <t>0.9795,0.0030,0.0076,0.0015</t>
+  </si>
+  <si>
+    <t>0.9471,0.0059,0.0261,0.0107</t>
+  </si>
+  <si>
+    <t>0.9493,0.0003,0.1170,0.0003</t>
+  </si>
+  <si>
+    <t>0.9131,0.0055,0.0706,0.0080</t>
+  </si>
+  <si>
+    <t>0.0674,0.0005,0.0013,0.9799</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.0006,0.9997</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.0028,0.9982</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.0006,0.9981</t>
+  </si>
+  <si>
+    <t>0.0046,0.8703,0.8345,0.0058</t>
+  </si>
+  <si>
+    <t>0.9932,0.0023,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.2185,0.8140,0.0078,0.0040</t>
+  </si>
+  <si>
+    <t>0.9916,0.0011,0.0008,0.0033</t>
+  </si>
+  <si>
+    <t>0.8447,0.1788,0.0079,0.0054</t>
+  </si>
+  <si>
+    <t>0.9949,0.0002,0.0004,0.0025</t>
+  </si>
+  <si>
+    <t>0.8951,0.0032,0.0039,0.1371</t>
+  </si>
+  <si>
+    <t>0.9944,0.0010,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.2801,0.9941,0.0032</t>
+  </si>
+  <si>
+    <t>0.9375,0.0005,0.0007,0.1072</t>
+  </si>
+  <si>
+    <t>0.9608,0.0059,0.0059,0.0170</t>
+  </si>
+  <si>
+    <t>0.2836,0.6747,0.0054,0.0253</t>
+  </si>
+  <si>
+    <t>0.9733,0.0099,0.0079,0.0017</t>
+  </si>
+  <si>
+    <t>0.9642,0.0135,0.0113,0.0035</t>
+  </si>
+  <si>
+    <t>0.1409,0.8002,0.0474,0.0178</t>
+  </si>
+  <si>
+    <t>0.9763,0.0153,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.8709,0.1554,0.0097,0.0047</t>
+  </si>
+  <si>
+    <t>0.9893,0.0008,0.0014,0.0063</t>
+  </si>
+  <si>
+    <t>0.9896,0.0014,0.0005,0.0053</t>
+  </si>
+  <si>
+    <t>0.9946,0.0009,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9951,0.0002,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.9923,0.0013,0.0025,0.0015</t>
+  </si>
+  <si>
+    <t>0.9931,0.0015,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9912,0.0011,0.0016,0.0033</t>
+  </si>
+  <si>
+    <t>0.9957,0.0004,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.8924,0.1056,0.0068,0.0068</t>
+  </si>
+  <si>
+    <t>0.5800,0.5563,0.0047,0.0021</t>
+  </si>
+  <si>
+    <t>0.7966,0.3639,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.1206,0.1821,0.8430,0.0031</t>
+  </si>
+  <si>
+    <t>0.9858,0.0137,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9235,0.0758,0.0173,0.0014</t>
+  </si>
+  <si>
+    <t>0.9873,0.0045,0.0024,0.0013</t>
+  </si>
+  <si>
+    <t>0.9868,0.0084,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0590,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.9487,0.0551,0.0052,0.0017</t>
+  </si>
+  <si>
+    <t>0.0073,0.0059,0.9893,0.0028</t>
+  </si>
+  <si>
+    <t>0.0043,0.0089,0.9902,0.0022</t>
+  </si>
+  <si>
+    <t>0.0014,0.0061,0.9964,0.0010</t>
+  </si>
+  <si>
+    <t>0.0258,0.0050,0.9749,0.0021</t>
+  </si>
+  <si>
+    <t>0.0035,0.0025,0.9924,0.0032</t>
+  </si>
+  <si>
+    <t>0.0088,0.0010,0.9935,0.0003</t>
+  </si>
+  <si>
+    <t>0.0063,0.0053,0.9896,0.0017</t>
+  </si>
+  <si>
+    <t>0.0289,0.0068,0.9646,0.0021</t>
+  </si>
+  <si>
+    <t>0.4937,0.0058,0.6312,0.0093</t>
+  </si>
+  <si>
+    <t>0.7152,0.0253,0.3452,0.0013</t>
+  </si>
+  <si>
+    <t>0.1770,0.3012,0.4507,0.0871</t>
+  </si>
+  <si>
+    <t>0.0309,0.1188,0.8869,0.0026</t>
+  </si>
+  <si>
+    <t>0.7854,0.0654,0.1150,0.0026</t>
+  </si>
+  <si>
+    <t>0.4714,0.0175,0.5427,0.0234</t>
+  </si>
+  <si>
+    <t>0.3483,0.0433,0.6545,0.0077</t>
+  </si>
+  <si>
+    <t>0.0663,0.9419,0.0049,0.0017</t>
+  </si>
+  <si>
+    <t>0.2821,0.8305,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9397,0.1174,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9678,0.0476,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.6623,0.5611,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.7637,0.0513,0.1975,0.0090</t>
+  </si>
+  <si>
+    <t>0.9643,0.0017,0.0170,0.0069</t>
+  </si>
+  <si>
+    <t>0.8105,0.0076,0.0948,0.0633</t>
+  </si>
+  <si>
+    <t>0.7414,0.1584,0.0845,0.0058</t>
+  </si>
+  <si>
+    <t>0.9302,0.0028,0.0352,0.0144</t>
+  </si>
+  <si>
+    <t>0.0012,0.0193,0.9917,0.0070</t>
+  </si>
+  <si>
+    <t>0.0301,0.0353,0.9284,0.0092</t>
+  </si>
+  <si>
+    <t>0.9470,0.0036,0.0647,0.0004</t>
+  </si>
+  <si>
+    <t>0.6264,0.0238,0.3525,0.0224</t>
+  </si>
+  <si>
+    <t>0.0063,0.0051,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0002,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9817,0.0103,0.0038,0.0022</t>
+  </si>
+  <si>
+    <t>0.9910,0.0019,0.0014,0.0024</t>
+  </si>
+  <si>
+    <t>0.9945,0.0021,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9868,0.0098,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9954,0.0009,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9804,0.0050,0.0012,0.0071</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0132,0.0153,0.9864,0.0017</t>
+  </si>
+  <si>
+    <t>0.2413,0.6909,0.1393,0.0178</t>
+  </si>
+  <si>
+    <t>0.8664,0.0086,0.0513,0.0592</t>
+  </si>
+  <si>
+    <t>0.0018,0.0305,0.9916,0.0027</t>
+  </si>
+  <si>
+    <t>0.0051,0.0136,0.9807,0.0170</t>
+  </si>
+  <si>
+    <t>0.1415,0.0834,0.8180,0.0209</t>
+  </si>
+  <si>
+    <t>0.0013,0.0007,0.9971,0.0013</t>
+  </si>
+  <si>
+    <t>0.0081,0.0020,0.9884,0.0010</t>
+  </si>
+  <si>
+    <t>0.0009,0.0013,0.9982,0.0006</t>
+  </si>
+  <si>
+    <t>0.0110,0.0054,0.9808,0.0029</t>
+  </si>
+  <si>
+    <t>0.0056,0.0159,0.9818,0.0022</t>
+  </si>
+  <si>
+    <t>0.8981,0.0122,0.1003,0.0050</t>
+  </si>
+  <si>
+    <t>0.7416,0.0046,0.4604,0.0013</t>
+  </si>
+  <si>
+    <t>0.9356,0.0112,0.0262,0.0078</t>
+  </si>
+  <si>
+    <t>0.9925,0.0021,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9942,0.0025,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9949,0.0016,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9918,0.0051,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9966,0.0009,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9885,0.0070,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9927,0.0051,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9944,0.0006,0.0002,0.0030</t>
+  </si>
+  <si>
+    <t>0.0100,0.1635,0.8637,0.0006</t>
+  </si>
+  <si>
+    <t>0.0054,0.0033,0.9935,0.0007</t>
+  </si>
+  <si>
+    <t>0.0041,0.0891,0.9836,0.0075</t>
+  </si>
+  <si>
+    <t>0.1557,0.0050,0.9119,0.0012</t>
+  </si>
+  <si>
+    <t>0.0037,0.0013,0.9926,0.0029</t>
+  </si>
+  <si>
+    <t>0.3402,0.0108,0.5948,0.0561</t>
+  </si>
+  <si>
+    <t>0.1094,0.0095,0.8970,0.0074</t>
+  </si>
+  <si>
+    <t>0.0030,0.0054,0.9831,0.0106</t>
+  </si>
+  <si>
+    <t>0.9597,0.0001,0.0007,0.0630</t>
+  </si>
+  <si>
+    <t>0.0200,0.0029,0.0005,0.9929</t>
+  </si>
+  <si>
+    <t>0.0488,0.0001,0.0006,0.9875</t>
+  </si>
+  <si>
+    <t>0.0034,0.0001,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.9512,0.0032,0.0011,0.0381</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
